--- a/ascend_test_suite/latest/model_list.xlsx
+++ b/ascend_test_suite/latest/model_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17230"/>
   </bookViews>
   <sheets>
     <sheet name="Ascend" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
     <t>910B1</t>
   </si>
   <si>
-    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --tool-call-parser deepseek_v3</t>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --gpu-memory-utilization 0.95 --tool-call-parser deepseek_v3</t>
   </si>
   <si>
     <t>长上下文场景可以加上参数--compute-mla-model-as-mha</t>
@@ -2779,7 +2779,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --tool-call-parser deepseek_" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5"/>
+    <hyperlink ref="C2" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model DeepSeek-R1-AWQ --tokenizer /home/weight/DeepSeek-R1-AWQ/ -tp 8 --port 4321 --platform-type ascend --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --quantization awq --swap-space 40 --gpu-memory-utilization 0.9" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/ascend_test_suite/latest/model_list.xlsx
+++ b/ascend_test_suite/latest/model_list.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="86">
   <si>
     <t>模型名称</t>
   </si>
@@ -48,6 +48,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7"   </t>
     </r>
     <r>
@@ -759,6 +766,12 @@
   </si>
   <si>
     <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Baichuan2-7B-Chat --tokenizer /home/weight/Baichuan2-7B-Chat -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40</t>
+  </si>
+  <si>
+    <t>Qwen3-32B-v2</t>
+  </si>
+  <si>
+    <t>docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/weight/:/home/weight/ -e "ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7" docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen3-32B-v2 --tokenizer /home/weight/Qwen3/Qwen3-32B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes --use-model-v2</t>
   </si>
 </sst>
 </file>
@@ -795,6 +808,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -956,11 +975,6 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1156,12 +1170,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1265,152 +1294,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1418,6 +1447,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1741,7 +1776,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2255,6 +2290,34 @@
         <v>83</v>
       </c>
     </row>
+    <row r="41" ht="14" spans="1:20">
+      <c r="A41" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C10" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot;  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5  --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000  --master-addr 0.0.0.0 --master-port 8008  --nnodes 1 --node-rank 0 --platform-type ascend  --swap-space 40 --tool-call-pars"/>
@@ -2272,6 +2335,7 @@
     <hyperlink ref="C33" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot;  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5  --model Qwen3-235B-A22B --tokenizer /home/weight/Qwen3/Qwen3-235B-A22B -tp 8 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 2048 --port 8000  --master-addr 0.0.0.0 --master-port 8008  --nnodes 1 --node-rank 0 --gpu-memory-utilization 0.981 --platform-type ascend  --swap-space 40 --too"/>
     <hyperlink ref="C7" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot;  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5   --model DeepSeek-R1-Distill-Qwen-1.5B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-1.5B -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000  --master-addr 0.0.0.0 --master-port 8008  --nnodes 1 --node-rank 0 --platform-type ascend  --swap-space 40 --tool-call-p"/>
     <hyperlink ref="C19" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm  --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/:/home/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot;  docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5  --model Qwen2.5-14B-Instruct --tokenizer /home/weight/Qwen2.5-14B-Instruct -tp 1 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000  --master-addr 0.0.0.0 --master-port 8008  --nnodes 1 --node-rank 0 --platform-type ascend  --swap-space 40 --tool-call-parser hermes"/>
+    <hyperlink ref="C41" r:id="rId1" display="docker run -it --name siginfer_serving --rm --privileged --device=/dev/davinci_manager --ipc=host --device=/dev/devmm_svm --device=/dev/hisi_hdc -v /usr/local/Ascend/driver/:/usr/local/Ascend/driver/:ro -v /usr/local/bin/npu-smi:/usr/local/bin/npu-smi -v /dev/davinci0:/dev/davinci0 -v /dev/davinci1:/dev/davinci1 -v /dev/davinci2:/dev/davinci2 -v /dev/davinci3:/dev/davinci3 -v /dev/davinci4:/dev/davinci4 -v /dev/davinci5:/dev/davinci5 -v /dev/davinci6:/dev/davinci6 -v /dev/davinci7:/dev/davinci7 --network host --pid host -u root -v /home/weight/:/home/weight/ -e &quot;ASCEND_RT_VISIBLE_DEVICES=0,1,2,3,4,5,6,7&quot; docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5 --model Qwen3-32B-v2 --tokenizer /home/weight/Qwen3/Qwen3-32B -tp 2 --block-size 128 --weight-dtype=FP16 --schedule-policy DynamicSplitFuseV2 --max-num-batched-tokens 8192 --port 8000 --master-addr 0.0.0.0 --master-port 8008 --nnodes 1 --node-rank 0 --platform-type ascend --swap-space 40 --tool-call-parser hermes --use-model" tooltip="http://docker.xcoresigma.com/docker/siginfer-aarch64-ascend:v1.2.rc5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
